--- a/public/fun/pack/xlsx/gift/경조사비장부_44_칠순·팔순중심_정월대보름달집.xlsx
+++ b/public/fun/pack/xlsx/gift/경조사비장부_44_칠순·팔순중심_정월대보름달집.xlsx
@@ -29,7 +29,7 @@
     <t>경조사비 장부 · 칠순·팔순 중심</t>
   </si>
   <si>
-    <t>“대보름 달 아래 빌어 준 소원들”</t>
+    <t>“집안 대소사 일정 기록”</t>
   </si>
   <si>
     <t>정월 대보름 달집 테마</t>

--- a/public/fun/pack/xlsx/gift/경조사비장부_44_칠순·팔순중심_정월대보름달집.xlsx
+++ b/public/fun/pack/xlsx/gift/경조사비장부_44_칠순·팔순중심_정월대보름달집.xlsx
@@ -24,12 +24,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="72">
   <si>
     <t>경조사비 장부 · 칠순·팔순 중심</t>
-  </si>
-  <si>
-    <t>“집안 대소사 일정 기록”</t>
   </si>
   <si>
     <t>정월 대보름 달집 테마</t>
@@ -1429,71 +1426,69 @@
       <c r="C2" s="1"/>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3"/>
     </row>
     <row r="5" spans="2:3" ht="6" customHeight="1"/>
     <row r="6" spans="2:3">
       <c r="B6" s="4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" s="5"/>
     </row>
     <row r="7" spans="2:3" ht="32" customHeight="1">
       <c r="B7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>4</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="32" customHeight="1">
       <c r="B8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>6</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="22" customHeight="1">
       <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>8</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="32" customHeight="1">
       <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>10</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="28" customHeight="1">
       <c r="B12" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="8"/>
     </row>
     <row r="13" spans="2:3" ht="28" customHeight="1">
       <c r="B13" s="8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C13" s="8"/>
     </row>
     <row r="15" spans="2:3">
       <c r="B15" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="9"/>
     </row>
@@ -1542,9 +1537,7 @@
       <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1555,28 +1548,28 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="F4" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="H4" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1584,25 +1577,25 @@
         <v>46027</v>
       </c>
       <c r="B5" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>44</v>
-      </c>
       <c r="E5" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="15">
         <v>50000</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1610,25 +1603,25 @@
         <v>46029</v>
       </c>
       <c r="B6" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>47</v>
-      </c>
       <c r="E6" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F6" s="15">
         <v>100000</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1636,25 +1629,25 @@
         <v>46062</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F7" s="15">
         <v>30000</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1662,25 +1655,25 @@
         <v>46064</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F8" s="15">
         <v>70000</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1688,25 +1681,25 @@
         <v>46094</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" s="15">
         <v>50000</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1714,25 +1707,25 @@
         <v>46096</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D10" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F10" s="15">
         <v>100000</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1740,25 +1733,25 @@
         <v>46129</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D11" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F11" s="15">
         <v>30000</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1766,25 +1759,25 @@
         <v>46131</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D12" s="14" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F12" s="15">
         <v>70000</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1792,25 +1785,25 @@
         <v>46163</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F13" s="15">
         <v>50000</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1818,25 +1811,25 @@
         <v>46165</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" s="15">
         <v>100000</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1844,25 +1837,25 @@
         <v>46198</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F15" s="15">
         <v>30000</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1870,25 +1863,25 @@
         <v>46200</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F16" s="15">
         <v>70000</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -6832,7 +6825,7 @@
   <sheetData>
     <row r="1" spans="2:11">
       <c r="B1" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" s="16"/>
       <c r="D1" s="16"/>
@@ -6846,31 +6839,31 @@
     </row>
     <row r="3" spans="2:11">
       <c r="B3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="I3" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="4" spans="2:11">
@@ -7199,7 +7192,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I12" s="20">
         <f>SUM(I4:I11)</f>
@@ -7216,7 +7209,7 @@
     </row>
     <row r="13" spans="2:11">
       <c r="B13" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="22">
         <f>SUM(C4:C12)</f>
@@ -7237,7 +7230,7 @@
     </row>
     <row r="15" spans="2:11">
       <c r="B15" s="23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C15" s="24">
         <f>COUNTIF('장부'!$G$5:$G$504,"필요")</f>
@@ -7270,21 +7263,21 @@
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C1" s="16"/>
     </row>
     <row r="3" spans="2:3">
       <c r="B3" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C3" s="25" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" s="23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" s="26">
         <f>SUMIFS('장부'!$F$5:$F$504,'장부'!$D$5:$D$504,$C$3,'장부'!$B$5:$B$504,"받음")</f>
@@ -7293,7 +7286,7 @@
     </row>
     <row r="6" spans="2:3">
       <c r="B6" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6" s="26">
         <f>SUMIFS('장부'!$F$5:$F$504,'장부'!$D$5:$D$504,$C$3,'장부'!$B$5:$B$504,"드림")</f>
@@ -7302,7 +7295,7 @@
     </row>
     <row r="7" spans="2:3">
       <c r="B7" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C7" s="27">
         <f>C5-C6</f>
@@ -7311,7 +7304,7 @@
     </row>
     <row r="8" spans="2:3">
       <c r="B8" s="23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C8" s="28">
         <f>COUNTIFS('장부'!$D$5:$D$504,$C$3,'장부'!$F$5:$F$504,"&gt;0")</f>
@@ -7320,7 +7313,7 @@
     </row>
     <row r="9" spans="2:3">
       <c r="B9" s="23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C9" s="12">
         <f>IF(C8=0,"",SUMPRODUCT(MAX(('장부'!$D$5:$D$504=$C$3)*'장부'!$A$5:$A$504)))</f>
@@ -7329,7 +7322,7 @@
     </row>
     <row r="10" spans="2:3">
       <c r="B10" s="23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C10" s="28">
         <f>COUNTIFS('장부'!$D$5:$D$504,$C$3,'장부'!$G$5:$G$504,"필요")</f>
@@ -7338,7 +7331,7 @@
     </row>
     <row r="12" spans="2:3">
       <c r="B12" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" s="8"/>
     </row>
@@ -7375,98 +7368,98 @@
   <sheetData>
     <row r="1" spans="2:4">
       <c r="B1" s="29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1" s="29"/>
       <c r="D1" s="29"/>
     </row>
     <row r="3" spans="2:4">
       <c r="B3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="D3" s="11" t="s">
         <v>17</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="30" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="2:4">
       <c r="B5" s="30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="2:4">
       <c r="B6" s="30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="2:4">
       <c r="B7" s="30" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:4">
       <c r="B8" s="30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="2:4">
       <c r="B9" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C9" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="2:4">
       <c r="B10" s="30" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C10" s="30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="2:4">
       <c r="B11" s="30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="30" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="2:4">
       <c r="B12" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
